--- a/data/availability/projects/travco-properties/almaza-bay.xlsx
+++ b/data/availability/projects/travco-properties/almaza-bay.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
